--- a/booking_analysis.xlsx
+++ b/booking_analysis.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;฿&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,11 +87,28 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001A7A34"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00AA6600"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +138,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FBFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -229,6 +256,45 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -236,16 +302,28 @@
     <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -613,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -738,41 +816,2221 @@
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
+          <t>brand new ozone bangtao condo by lofty</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="20" t="n">
+        <v>7372</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>8191</v>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>-18.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="25" t="inlineStr"/>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="27" t="n">
+        <v>8203</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>9115</v>
+      </c>
+      <c r="F6" s="29" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G6" s="30" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 18 July 2026</t>
+        </is>
+      </c>
+      <c r="H6" s="31" t="inlineStr">
+        <is>
+          <t>-9.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>the ozone bangtao by beringela</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>7484</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>8316</v>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>-17.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>ozone apartment in lagune</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>12700</v>
+      </c>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="22" t="inlineStr"/>
+      <c r="G8" s="32" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 2 July 2026</t>
+        </is>
+      </c>
+      <c r="H8" s="33" t="inlineStr">
+        <is>
+          <t>+39.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="25" t="inlineStr"/>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>13750</v>
+      </c>
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="29" t="inlineStr"/>
+      <c r="G9" s="30" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 27 July 2026</t>
+        </is>
+      </c>
+      <c r="H9" s="34" t="inlineStr">
+        <is>
+          <t>+51.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>cozy 1 br bangtao beach</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>14204</v>
+      </c>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="22" t="inlineStr"/>
+      <c r="G10" s="32" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 27 July 2026</t>
+        </is>
+      </c>
+      <c r="H10" s="33" t="inlineStr">
+        <is>
+          <t>+56.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="25" t="inlineStr"/>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>15554</v>
+      </c>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="29" t="inlineStr"/>
+      <c r="G11" s="30" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation anytime</t>
+        </is>
+      </c>
+      <c r="H11" s="34" t="inlineStr">
+        <is>
+          <t>+71.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>stylish-one-bedroom-apartment-in-ozone-condominium</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>14707</v>
+      </c>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="22" t="inlineStr"/>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t>✓ Partially refundable</t>
+        </is>
+      </c>
+      <c r="H12" s="33" t="inlineStr">
+        <is>
+          <t>+62.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>brand new 1br ozone condo panoramic windows 8557</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>16400</v>
+      </c>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="22" t="inlineStr"/>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H13" s="33" t="inlineStr">
+        <is>
+          <t>+80.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>new spacious condo 1br 42m2 ozone bangtao 8686</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>16400</v>
+      </c>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="22" t="inlineStr"/>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H14" s="33" t="inlineStr">
+        <is>
+          <t>+80.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>ozone condominium bang tao by my home phuket</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>16940</v>
+      </c>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="22" t="inlineStr"/>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H15" s="33" t="inlineStr">
+        <is>
+          <t>+86.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>c231 brand new 1br prime spot pool amp gym near beach</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="20" t="n">
+        <v>17609</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>19393</v>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H16" s="33" t="inlineStr">
+        <is>
+          <t>+93.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
           <t>C235 New Modern 1BR</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>One-Bedroom Apartment</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="20" t="n">
+      <c r="C17" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="20" t="n">
         <v>19628</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E17" s="21" t="n">
         <v>24148</v>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>-19%</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>✗ Non-refundable</t>
         </is>
       </c>
-      <c r="H5" s="24" t="inlineStr">
+      <c r="H17" s="33" t="inlineStr">
         <is>
           <t>+116.1%</t>
         </is>
       </c>
     </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>📅  2026-09-01 → 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Тип номера / Тариф</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Гостей</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Цена ฿</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>До скидки ฿</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Скидка %</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Возвратность</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>vs Мой мин %</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>★ Ozone 1BR</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment with Balcony</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>7947</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>8697</v>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="11" t="inlineStr"/>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>8697</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>9530</v>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 2 August 2026</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>brand new ozone bangtao condo by lofty</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="20" t="n">
+        <v>7194</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>7993</v>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>-9.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="25" t="inlineStr"/>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="27" t="n">
+        <v>8025</v>
+      </c>
+      <c r="E25" s="28" t="n">
+        <v>8917</v>
+      </c>
+      <c r="F25" s="29" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G25" s="30" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 18 August 2026</t>
+        </is>
+      </c>
+      <c r="H25" s="34" t="inlineStr">
+        <is>
+          <t>+1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>the ozone bangtao by beringela</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="20" t="n">
+        <v>7484</v>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>8316</v>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G26" s="32" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 3 July 2026</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>-5.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>ozone apartment in lagune</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>12700</v>
+      </c>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="22" t="inlineStr"/>
+      <c r="G27" s="32" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 2 August 2026</t>
+        </is>
+      </c>
+      <c r="H27" s="33" t="inlineStr">
+        <is>
+          <t>+59.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="25" t="inlineStr"/>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="27" t="n">
+        <v>13750</v>
+      </c>
+      <c r="E28" s="26" t="n"/>
+      <c r="F28" s="29" t="inlineStr"/>
+      <c r="G28" s="30" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 27 August 2026</t>
+        </is>
+      </c>
+      <c r="H28" s="34" t="inlineStr">
+        <is>
+          <t>+73.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>cozy 1 br bangtao beach</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>14344</v>
+      </c>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="22" t="inlineStr"/>
+      <c r="G29" s="32" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 27 August 2026</t>
+        </is>
+      </c>
+      <c r="H29" s="33" t="inlineStr">
+        <is>
+          <t>+80.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="25" t="inlineStr"/>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="27" t="n">
+        <v>15709</v>
+      </c>
+      <c r="E30" s="26" t="n"/>
+      <c r="F30" s="29" t="inlineStr"/>
+      <c r="G30" s="30" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation anytime</t>
+        </is>
+      </c>
+      <c r="H30" s="34" t="inlineStr">
+        <is>
+          <t>+97.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>stylish-one-bedroom-apartment-in-ozone-condominium</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>14707</v>
+      </c>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="22" t="inlineStr"/>
+      <c r="G31" s="32" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 3 July 2026</t>
+        </is>
+      </c>
+      <c r="H31" s="33" t="inlineStr">
+        <is>
+          <t>+85.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>ozone condominium bang tao by my home phuket</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="20" t="n">
+        <v>16940</v>
+      </c>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="22" t="inlineStr"/>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H32" s="33" t="inlineStr">
+        <is>
+          <t>+113.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>C235 New Modern 1BR</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>17410</v>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>21375</v>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>-19%</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H33" s="33" t="inlineStr">
+        <is>
+          <t>+119.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>c231 brand new 1br prime spot pool amp gym near beach</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>19241</v>
+      </c>
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="22" t="inlineStr"/>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H34" s="33" t="inlineStr">
+        <is>
+          <t>+142.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>brand new 1br ozone condo panoramic windows 8557</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="20" t="n">
+        <v>23400</v>
+      </c>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="22" t="inlineStr"/>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H35" s="33" t="inlineStr">
+        <is>
+          <t>+194.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>new spacious condo 1br 42m2 ozone bangtao 8686</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>23400</v>
+      </c>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="22" t="inlineStr"/>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H36" s="33" t="inlineStr">
+        <is>
+          <t>+194.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>📅  2026-10-01 → 2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Тип номера / Тариф</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Гостей</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Цена ฿</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>До скидки ฿</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Скидка %</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Возвратность</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>vs Мой мин %</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>★ Ozone 1BR</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment with Balcony</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>14184</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>15627</v>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="11" t="inlineStr"/>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>15627</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>17230</v>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 1 September 2026</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="inlineStr"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>the ozone bangtao by beringela</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>7484</v>
+      </c>
+      <c r="E43" s="21" t="n">
+        <v>8316</v>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G43" s="32" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 2 August 2026</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>-47.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>brand new ozone bangtao condo by lofty</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="20" t="n">
+        <v>11381</v>
+      </c>
+      <c r="E44" s="21" t="n">
+        <v>12646</v>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H44" s="24" t="inlineStr">
+        <is>
+          <t>-19.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="25" t="inlineStr"/>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="27" t="n">
+        <v>12599</v>
+      </c>
+      <c r="E45" s="28" t="n">
+        <v>13999</v>
+      </c>
+      <c r="F45" s="29" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G45" s="30" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 17 September 2026</t>
+        </is>
+      </c>
+      <c r="H45" s="31" t="inlineStr">
+        <is>
+          <t>-11.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>ozone apartment in lagune</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" s="20" t="n">
+        <v>14800</v>
+      </c>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="22" t="inlineStr"/>
+      <c r="G46" s="32" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 1 September 2026</t>
+        </is>
+      </c>
+      <c r="H46" s="33" t="inlineStr">
+        <is>
+          <t>+4.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="25" t="inlineStr"/>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="27" t="n">
+        <v>16060</v>
+      </c>
+      <c r="E47" s="26" t="n"/>
+      <c r="F47" s="29" t="inlineStr"/>
+      <c r="G47" s="30" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 26 September 2026</t>
+        </is>
+      </c>
+      <c r="H47" s="34" t="inlineStr">
+        <is>
+          <t>+13.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>c231 brand new 1br prime spot pool amp gym near beach</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="20" t="n">
+        <v>16654</v>
+      </c>
+      <c r="E48" s="21" t="n">
+        <v>18333</v>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H48" s="33" t="inlineStr">
+        <is>
+          <t>+17.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>ozone condominium bang tao by my home phuket</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" s="20" t="n">
+        <v>16940</v>
+      </c>
+      <c r="E49" s="19" t="n"/>
+      <c r="F49" s="22" t="inlineStr"/>
+      <c r="G49" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H49" s="33" t="inlineStr">
+        <is>
+          <t>+19.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>C235 New Modern 1BR</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="20" t="n">
+        <v>17410</v>
+      </c>
+      <c r="E50" s="21" t="n">
+        <v>21375</v>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>-19%</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H50" s="33" t="inlineStr">
+        <is>
+          <t>+22.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>stylish-one-bedroom-apartment-in-ozone-condominium</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="20" t="n">
+        <v>18123</v>
+      </c>
+      <c r="E51" s="19" t="n"/>
+      <c r="F51" s="22" t="inlineStr"/>
+      <c r="G51" s="32" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 2 August 2026</t>
+        </is>
+      </c>
+      <c r="H51" s="33" t="inlineStr">
+        <is>
+          <t>+27.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>cozy 1 br bangtao beach</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="20" t="n">
+        <v>20339</v>
+      </c>
+      <c r="E52" s="21" t="n">
+        <v>22573</v>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G52" s="32" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 26 September 2026</t>
+        </is>
+      </c>
+      <c r="H52" s="33" t="inlineStr">
+        <is>
+          <t>+43.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>brand new 1br ozone condo panoramic windows 8557</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="20" t="n">
+        <v>30400</v>
+      </c>
+      <c r="E53" s="19" t="n"/>
+      <c r="F53" s="22" t="inlineStr"/>
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H53" s="33" t="inlineStr">
+        <is>
+          <t>+114.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>new spacious condo 1br 42m2 ozone bangtao 8686</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="20" t="n">
+        <v>30400</v>
+      </c>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="22" t="inlineStr"/>
+      <c r="G54" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H54" s="33" t="inlineStr">
+        <is>
+          <t>+114.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>📅  2026-11-01 → 2026-11-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Тип номера / Тариф</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Гостей</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Цена ฿</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>До скидки ฿</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Скидка %</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Возвратность</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>vs Мой мин %</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>★ Ozone 1BR</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment with Balcony</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>16032</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>17230</v>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr"/>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>the ozone bangtao by beringela</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="20" t="n">
+        <v>16632</v>
+      </c>
+      <c r="E60" s="21" t="n">
+        <v>18480</v>
+      </c>
+      <c r="F60" s="22" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G60" s="32" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 2 September 2026</t>
+        </is>
+      </c>
+      <c r="H60" s="33" t="inlineStr">
+        <is>
+          <t>+3.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>brand new ozone bangtao condo by lofty</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="20" t="n">
+        <v>20298</v>
+      </c>
+      <c r="E61" s="21" t="n">
+        <v>22553</v>
+      </c>
+      <c r="F61" s="22" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H61" s="33" t="inlineStr">
+        <is>
+          <t>+26.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="25" t="inlineStr"/>
+      <c r="B62" s="25" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="27" t="n">
+        <v>22555</v>
+      </c>
+      <c r="E62" s="28" t="n">
+        <v>25061</v>
+      </c>
+      <c r="F62" s="29" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G62" s="30" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 18 October 2026</t>
+        </is>
+      </c>
+      <c r="H62" s="34" t="inlineStr">
+        <is>
+          <t>+40.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>cozy 1 br bangtao beach</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="20" t="n">
+        <v>28688</v>
+      </c>
+      <c r="E63" s="19" t="n"/>
+      <c r="F63" s="22" t="inlineStr"/>
+      <c r="G63" s="32" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 27 October 2026</t>
+        </is>
+      </c>
+      <c r="H63" s="33" t="inlineStr">
+        <is>
+          <t>+78.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>C235 New Modern 1BR</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C64" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="20" t="n">
+        <v>32223</v>
+      </c>
+      <c r="E64" s="21" t="n">
+        <v>39892</v>
+      </c>
+      <c r="F64" s="22" t="inlineStr">
+        <is>
+          <t>-19%</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H64" s="33" t="inlineStr">
+        <is>
+          <t>+101.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>ozone condominium bang tao by my home phuket</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C65" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="20" t="n">
+        <v>32606</v>
+      </c>
+      <c r="E65" s="19" t="n"/>
+      <c r="F65" s="22" t="inlineStr"/>
+      <c r="G65" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H65" s="33" t="inlineStr">
+        <is>
+          <t>+103.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>c231 brand new 1br prime spot pool amp gym near beach</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" s="20" t="n">
+        <v>34869</v>
+      </c>
+      <c r="E66" s="19" t="n"/>
+      <c r="F66" s="22" t="inlineStr"/>
+      <c r="G66" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H66" s="33" t="inlineStr">
+        <is>
+          <t>+117.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>brand new 1br ozone condo panoramic windows 8557</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C67" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" s="20" t="n">
+        <v>36700</v>
+      </c>
+      <c r="E67" s="19" t="n"/>
+      <c r="F67" s="22" t="inlineStr"/>
+      <c r="G67" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H67" s="33" t="inlineStr">
+        <is>
+          <t>+128.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>new spacious condo 1br 42m2 ozone bangtao 8686</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="20" t="n">
+        <v>36700</v>
+      </c>
+      <c r="E68" s="19" t="n"/>
+      <c r="F68" s="22" t="inlineStr"/>
+      <c r="G68" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H68" s="33" t="inlineStr">
+        <is>
+          <t>+128.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="35" t="inlineStr">
+        <is>
+          <t>ozone apartment in lagune</t>
+        </is>
+      </c>
+      <c r="B69" s="35" t="inlineStr">
+        <is>
+          <t>— no_room_table</t>
+        </is>
+      </c>
+      <c r="C69" s="36" t="inlineStr"/>
+      <c r="D69" s="36" t="inlineStr"/>
+      <c r="E69" s="36" t="inlineStr"/>
+      <c r="F69" s="36" t="inlineStr"/>
+      <c r="G69" s="36" t="inlineStr"/>
+      <c r="H69" s="36" t="inlineStr"/>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="35" t="inlineStr">
+        <is>
+          <t>stylish-one-bedroom-apartment-in-ozone-condominium</t>
+        </is>
+      </c>
+      <c r="B70" s="35" t="inlineStr">
+        <is>
+          <t>— no_room_table</t>
+        </is>
+      </c>
+      <c r="C70" s="36" t="inlineStr"/>
+      <c r="D70" s="36" t="inlineStr"/>
+      <c r="E70" s="36" t="inlineStr"/>
+      <c r="F70" s="36" t="inlineStr"/>
+      <c r="G70" s="36" t="inlineStr"/>
+      <c r="H70" s="36" t="inlineStr"/>
+    </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>📅  2026-12-01 → 2026-12-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Тип номера / Тариф</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Гостей</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Цена ฿</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>До скидки ฿</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Скидка %</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Возвратность</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>vs Мой мин %</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="17" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>★ Ozone 1BR</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment with Balcony</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>25630</v>
+      </c>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="8" t="inlineStr"/>
+      <c r="G75" s="37" t="inlineStr">
+        <is>
+          <t>Flexible to reschedule if plans change</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr"/>
+    </row>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>brand new ozone bangtao condo by lofty</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C76" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" s="20" t="n">
+        <v>21783</v>
+      </c>
+      <c r="E76" s="21" t="n">
+        <v>24203</v>
+      </c>
+      <c r="F76" s="22" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H76" s="24" t="inlineStr">
+        <is>
+          <t>-15.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="25" t="inlineStr"/>
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="C77" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" s="27" t="n">
+        <v>24159</v>
+      </c>
+      <c r="E77" s="28" t="n">
+        <v>26843</v>
+      </c>
+      <c r="F77" s="29" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 17 November 2026</t>
+        </is>
+      </c>
+      <c r="H77" s="31" t="inlineStr">
+        <is>
+          <t>-5.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="17" customHeight="1">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>the ozone bangtao by beringela</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="20" t="n">
+        <v>27027</v>
+      </c>
+      <c r="E78" s="21" t="n">
+        <v>30030</v>
+      </c>
+      <c r="F78" s="22" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>✓ Free cancellation before 2 October 2026</t>
+        </is>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>+5.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="17" customHeight="1">
+      <c r="A79" s="18" t="inlineStr">
+        <is>
+          <t>ozone condominium bang tao by my home phuket</t>
+        </is>
+      </c>
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" s="20" t="n">
+        <v>32606</v>
+      </c>
+      <c r="E79" s="19" t="n"/>
+      <c r="F79" s="22" t="inlineStr"/>
+      <c r="G79" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>+27.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="17" customHeight="1">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>C235 New Modern 1BR</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C80" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" s="20" t="n">
+        <v>35394</v>
+      </c>
+      <c r="E80" s="21" t="n">
+        <v>43854</v>
+      </c>
+      <c r="F80" s="22" t="inlineStr">
+        <is>
+          <t>-19%</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H80" s="33" t="inlineStr">
+        <is>
+          <t>+38.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>brand new 1br ozone condo panoramic windows 8557</t>
+        </is>
+      </c>
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C81" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" s="20" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E81" s="19" t="n"/>
+      <c r="F81" s="22" t="inlineStr"/>
+      <c r="G81" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>+62.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>new spacious condo 1br 42m2 ozone bangtao 8686</t>
+        </is>
+      </c>
+      <c r="B82" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C82" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" s="20" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E82" s="19" t="n"/>
+      <c r="F82" s="22" t="inlineStr"/>
+      <c r="G82" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>+62.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" s="18" t="inlineStr">
+        <is>
+          <t>c231 brand new 1br prime spot pool amp gym near beach</t>
+        </is>
+      </c>
+      <c r="B83" s="18" t="inlineStr">
+        <is>
+          <t>One-Bedroom Apartment</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" s="20" t="n">
+        <v>48129</v>
+      </c>
+      <c r="E83" s="19" t="n"/>
+      <c r="F83" s="22" t="inlineStr"/>
+      <c r="G83" s="23" t="inlineStr">
+        <is>
+          <t>✗ Non-refundable</t>
+        </is>
+      </c>
+      <c r="H83" s="33" t="inlineStr">
+        <is>
+          <t>+87.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" s="35" t="inlineStr">
+        <is>
+          <t>cozy 1 br bangtao beach</t>
+        </is>
+      </c>
+      <c r="B84" s="35" t="inlineStr">
+        <is>
+          <t>— no_room_table</t>
+        </is>
+      </c>
+      <c r="C84" s="36" t="inlineStr"/>
+      <c r="D84" s="36" t="inlineStr"/>
+      <c r="E84" s="36" t="inlineStr"/>
+      <c r="F84" s="36" t="inlineStr"/>
+      <c r="G84" s="36" t="inlineStr"/>
+      <c r="H84" s="36" t="inlineStr"/>
+    </row>
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="35" t="inlineStr">
+        <is>
+          <t>ozone apartment in lagune</t>
+        </is>
+      </c>
+      <c r="B85" s="35" t="inlineStr">
+        <is>
+          <t>— no_room_table</t>
+        </is>
+      </c>
+      <c r="C85" s="36" t="inlineStr"/>
+      <c r="D85" s="36" t="inlineStr"/>
+      <c r="E85" s="36" t="inlineStr"/>
+      <c r="F85" s="36" t="inlineStr"/>
+      <c r="G85" s="36" t="inlineStr"/>
+      <c r="H85" s="36" t="inlineStr"/>
+    </row>
+    <row r="86" ht="17" customHeight="1">
+      <c r="A86" s="35" t="inlineStr">
+        <is>
+          <t>stylish-one-bedroom-apartment-in-ozone-condominium</t>
+        </is>
+      </c>
+      <c r="B86" s="35" t="inlineStr">
+        <is>
+          <t>— no_room_table</t>
+        </is>
+      </c>
+      <c r="C86" s="36" t="inlineStr"/>
+      <c r="D86" s="36" t="inlineStr"/>
+      <c r="E86" s="36" t="inlineStr"/>
+      <c r="F86" s="36" t="inlineStr"/>
+      <c r="G86" s="36" t="inlineStr"/>
+      <c r="H86" s="36" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -785,7 +3043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -798,37 +3056,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="38" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="38" t="inlineStr">
         <is>
           <t>Мин ฿</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="38" t="inlineStr">
         <is>
           <t>Макс ฿</t>
         </is>
       </c>
-      <c r="E1" s="25" t="inlineStr">
+      <c r="E1" s="38" t="inlineStr">
         <is>
           <t>Тарифов</t>
         </is>
       </c>
-      <c r="F1" s="25" t="inlineStr">
+      <c r="F1" s="38" t="inlineStr">
         <is>
           <t>Со скидкой</t>
         </is>
       </c>
-      <c r="G1" s="25" t="inlineStr">
+      <c r="G1" s="38" t="inlineStr">
         <is>
           <t>vs Мой мин %</t>
         </is>
@@ -840,15 +3098,15 @@
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>★ Ozone 1BR</t>
         </is>
       </c>
-      <c r="C2" s="27" t="n">
+      <c r="C2" s="40" t="n">
         <v>9081</v>
       </c>
-      <c r="D2" s="27" t="n">
+      <c r="D2" s="40" t="n">
         <v>9957</v>
       </c>
       <c r="E2" s="10" t="n">
@@ -860,33 +3118,1448 @@
       <c r="G2" s="10" t="inlineStr"/>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
+        <is>
+          <t>brand new ozone bangtao condo by lofty</t>
+        </is>
+      </c>
+      <c r="C3" s="43" t="n">
+        <v>7372</v>
+      </c>
+      <c r="D3" s="43" t="n">
+        <v>8203</v>
+      </c>
+      <c r="E3" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="44" t="inlineStr">
+        <is>
+          <t>-18.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>the ozone bangtao by beringela</t>
+        </is>
+      </c>
+      <c r="C4" s="45" t="n">
+        <v>7484</v>
+      </c>
+      <c r="D4" s="45" t="n">
+        <v>7484</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="46" t="inlineStr">
+        <is>
+          <t>-17.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="inlineStr">
+        <is>
+          <t>ozone apartment in lagune</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="n">
+        <v>12700</v>
+      </c>
+      <c r="D5" s="43" t="n">
+        <v>13750</v>
+      </c>
+      <c r="E5" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="41" t="inlineStr"/>
+      <c r="G5" s="47" t="inlineStr">
+        <is>
+          <t>+39.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>cozy 1 br bangtao beach</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="n">
+        <v>14204</v>
+      </c>
+      <c r="D6" s="45" t="n">
+        <v>15554</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="19" t="inlineStr"/>
+      <c r="G6" s="48" t="inlineStr">
+        <is>
+          <t>+56.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="inlineStr">
+        <is>
+          <t>stylish-one-bedroom-apartment-in-ozone-condominium</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="n">
+        <v>14707</v>
+      </c>
+      <c r="D7" s="43" t="n">
+        <v>14707</v>
+      </c>
+      <c r="E7" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="41" t="inlineStr"/>
+      <c r="G7" s="47" t="inlineStr">
+        <is>
+          <t>+62.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>brand new 1br ozone condo panoramic windows 8557</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="n">
+        <v>16400</v>
+      </c>
+      <c r="D8" s="45" t="n">
+        <v>16400</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="48" t="inlineStr">
+        <is>
+          <t>+80.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B9" s="42" t="inlineStr">
+        <is>
+          <t>new spacious condo 1br 42m2 ozone bangtao 8686</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="n">
+        <v>16400</v>
+      </c>
+      <c r="D9" s="43" t="n">
+        <v>16400</v>
+      </c>
+      <c r="E9" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="41" t="inlineStr"/>
+      <c r="G9" s="47" t="inlineStr">
+        <is>
+          <t>+80.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>ozone condominium bang tao by my home phuket</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="n">
+        <v>16940</v>
+      </c>
+      <c r="D10" s="45" t="n">
+        <v>16940</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="48" t="inlineStr">
+        <is>
+          <t>+86.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>c231 brand new 1br prime spot pool amp gym near beach</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="n">
+        <v>17609</v>
+      </c>
+      <c r="D11" s="43" t="n">
+        <v>17609</v>
+      </c>
+      <c r="E11" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="47" t="inlineStr">
+        <is>
+          <t>+93.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>C235 New Modern 1BR</t>
         </is>
       </c>
-      <c r="C3" s="30" t="n">
+      <c r="C12" s="45" t="n">
         <v>19628</v>
       </c>
-      <c r="D3" s="30" t="n">
+      <c r="D12" s="45" t="n">
         <v>19628</v>
       </c>
-      <c r="E3" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="31" t="inlineStr">
+      <c r="E12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="48" t="inlineStr">
         <is>
           <t>+116.1%</t>
         </is>
       </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>★ Ozone 1BR</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="n">
+        <v>7947</v>
+      </c>
+      <c r="D14" s="40" t="n">
+        <v>8697</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="inlineStr">
+        <is>
+          <t>brand new ozone bangtao condo by lofty</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="n">
+        <v>7194</v>
+      </c>
+      <c r="D15" s="43" t="n">
+        <v>8025</v>
+      </c>
+      <c r="E15" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="44" t="inlineStr">
+        <is>
+          <t>-9.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>the ozone bangtao by beringela</t>
+        </is>
+      </c>
+      <c r="C16" s="45" t="n">
+        <v>7484</v>
+      </c>
+      <c r="D16" s="45" t="n">
+        <v>7484</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="46" t="inlineStr">
+        <is>
+          <t>-5.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>ozone apartment in lagune</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="n">
+        <v>12700</v>
+      </c>
+      <c r="D17" s="43" t="n">
+        <v>13750</v>
+      </c>
+      <c r="E17" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="41" t="inlineStr"/>
+      <c r="G17" s="47" t="inlineStr">
+        <is>
+          <t>+59.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>cozy 1 br bangtao beach</t>
+        </is>
+      </c>
+      <c r="C18" s="45" t="n">
+        <v>14344</v>
+      </c>
+      <c r="D18" s="45" t="n">
+        <v>15709</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="19" t="inlineStr"/>
+      <c r="G18" s="48" t="inlineStr">
+        <is>
+          <t>+80.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="inlineStr">
+        <is>
+          <t>stylish-one-bedroom-apartment-in-ozone-condominium</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="n">
+        <v>14707</v>
+      </c>
+      <c r="D19" s="43" t="n">
+        <v>14707</v>
+      </c>
+      <c r="E19" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="41" t="inlineStr"/>
+      <c r="G19" s="47" t="inlineStr">
+        <is>
+          <t>+85.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>ozone condominium bang tao by my home phuket</t>
+        </is>
+      </c>
+      <c r="C20" s="45" t="n">
+        <v>16940</v>
+      </c>
+      <c r="D20" s="45" t="n">
+        <v>16940</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="19" t="inlineStr"/>
+      <c r="G20" s="48" t="inlineStr">
+        <is>
+          <t>+113.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>C235 New Modern 1BR</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="n">
+        <v>17410</v>
+      </c>
+      <c r="D21" s="43" t="n">
+        <v>17410</v>
+      </c>
+      <c r="E21" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="47" t="inlineStr">
+        <is>
+          <t>+119.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>c231 brand new 1br prime spot pool amp gym near beach</t>
+        </is>
+      </c>
+      <c r="C22" s="45" t="n">
+        <v>19241</v>
+      </c>
+      <c r="D22" s="45" t="n">
+        <v>19241</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="19" t="inlineStr"/>
+      <c r="G22" s="48" t="inlineStr">
+        <is>
+          <t>+142.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="41" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>brand new 1br ozone condo panoramic windows 8557</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="n">
+        <v>23400</v>
+      </c>
+      <c r="D23" s="43" t="n">
+        <v>23400</v>
+      </c>
+      <c r="E23" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="41" t="inlineStr"/>
+      <c r="G23" s="47" t="inlineStr">
+        <is>
+          <t>+194.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>new spacious condo 1br 42m2 ozone bangtao 8686</t>
+        </is>
+      </c>
+      <c r="C24" s="45" t="n">
+        <v>23400</v>
+      </c>
+      <c r="D24" s="45" t="n">
+        <v>23400</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="19" t="inlineStr"/>
+      <c r="G24" s="48" t="inlineStr">
+        <is>
+          <t>+194.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>★ Ozone 1BR</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="n">
+        <v>14184</v>
+      </c>
+      <c r="D26" s="40" t="n">
+        <v>15627</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B27" s="42" t="inlineStr">
+        <is>
+          <t>the ozone bangtao by beringela</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="n">
+        <v>7484</v>
+      </c>
+      <c r="D27" s="43" t="n">
+        <v>7484</v>
+      </c>
+      <c r="E27" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="44" t="inlineStr">
+        <is>
+          <t>-47.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>brand new ozone bangtao condo by lofty</t>
+        </is>
+      </c>
+      <c r="C28" s="45" t="n">
+        <v>11381</v>
+      </c>
+      <c r="D28" s="45" t="n">
+        <v>12599</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="46" t="inlineStr">
+        <is>
+          <t>-19.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B29" s="42" t="inlineStr">
+        <is>
+          <t>ozone apartment in lagune</t>
+        </is>
+      </c>
+      <c r="C29" s="43" t="n">
+        <v>14800</v>
+      </c>
+      <c r="D29" s="43" t="n">
+        <v>16060</v>
+      </c>
+      <c r="E29" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="41" t="inlineStr"/>
+      <c r="G29" s="47" t="inlineStr">
+        <is>
+          <t>+4.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>c231 brand new 1br prime spot pool amp gym near beach</t>
+        </is>
+      </c>
+      <c r="C30" s="45" t="n">
+        <v>16654</v>
+      </c>
+      <c r="D30" s="45" t="n">
+        <v>16654</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="48" t="inlineStr">
+        <is>
+          <t>+17.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B31" s="42" t="inlineStr">
+        <is>
+          <t>ozone condominium bang tao by my home phuket</t>
+        </is>
+      </c>
+      <c r="C31" s="43" t="n">
+        <v>16940</v>
+      </c>
+      <c r="D31" s="43" t="n">
+        <v>16940</v>
+      </c>
+      <c r="E31" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="41" t="inlineStr"/>
+      <c r="G31" s="47" t="inlineStr">
+        <is>
+          <t>+19.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>C235 New Modern 1BR</t>
+        </is>
+      </c>
+      <c r="C32" s="45" t="n">
+        <v>17410</v>
+      </c>
+      <c r="D32" s="45" t="n">
+        <v>17410</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="48" t="inlineStr">
+        <is>
+          <t>+22.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B33" s="42" t="inlineStr">
+        <is>
+          <t>stylish-one-bedroom-apartment-in-ozone-condominium</t>
+        </is>
+      </c>
+      <c r="C33" s="43" t="n">
+        <v>18123</v>
+      </c>
+      <c r="D33" s="43" t="n">
+        <v>18123</v>
+      </c>
+      <c r="E33" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="41" t="inlineStr"/>
+      <c r="G33" s="47" t="inlineStr">
+        <is>
+          <t>+27.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>cozy 1 br bangtao beach</t>
+        </is>
+      </c>
+      <c r="C34" s="45" t="n">
+        <v>20339</v>
+      </c>
+      <c r="D34" s="45" t="n">
+        <v>20339</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="48" t="inlineStr">
+        <is>
+          <t>+43.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B35" s="42" t="inlineStr">
+        <is>
+          <t>brand new 1br ozone condo panoramic windows 8557</t>
+        </is>
+      </c>
+      <c r="C35" s="43" t="n">
+        <v>30400</v>
+      </c>
+      <c r="D35" s="43" t="n">
+        <v>30400</v>
+      </c>
+      <c r="E35" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="41" t="inlineStr"/>
+      <c r="G35" s="47" t="inlineStr">
+        <is>
+          <t>+114.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>new spacious condo 1br 42m2 ozone bangtao 8686</t>
+        </is>
+      </c>
+      <c r="C36" s="45" t="n">
+        <v>30400</v>
+      </c>
+      <c r="D36" s="45" t="n">
+        <v>30400</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="19" t="inlineStr"/>
+      <c r="G36" s="48" t="inlineStr">
+        <is>
+          <t>+114.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="B38" s="39" t="inlineStr">
+        <is>
+          <t>★ Ozone 1BR</t>
+        </is>
+      </c>
+      <c r="C38" s="40" t="n">
+        <v>16032</v>
+      </c>
+      <c r="D38" s="40" t="n">
+        <v>16032</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="41" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="B39" s="42" t="inlineStr">
+        <is>
+          <t>the ozone bangtao by beringela</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="n">
+        <v>16632</v>
+      </c>
+      <c r="D39" s="43" t="n">
+        <v>16632</v>
+      </c>
+      <c r="E39" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="47" t="inlineStr">
+        <is>
+          <t>+3.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>brand new ozone bangtao condo by lofty</t>
+        </is>
+      </c>
+      <c r="C40" s="45" t="n">
+        <v>20298</v>
+      </c>
+      <c r="D40" s="45" t="n">
+        <v>22555</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="48" t="inlineStr">
+        <is>
+          <t>+26.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="41" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="B41" s="42" t="inlineStr">
+        <is>
+          <t>cozy 1 br bangtao beach</t>
+        </is>
+      </c>
+      <c r="C41" s="43" t="n">
+        <v>28688</v>
+      </c>
+      <c r="D41" s="43" t="n">
+        <v>28688</v>
+      </c>
+      <c r="E41" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="41" t="inlineStr"/>
+      <c r="G41" s="47" t="inlineStr">
+        <is>
+          <t>+78.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>C235 New Modern 1BR</t>
+        </is>
+      </c>
+      <c r="C42" s="45" t="n">
+        <v>32223</v>
+      </c>
+      <c r="D42" s="45" t="n">
+        <v>32223</v>
+      </c>
+      <c r="E42" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="48" t="inlineStr">
+        <is>
+          <t>+101.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="B43" s="42" t="inlineStr">
+        <is>
+          <t>ozone condominium bang tao by my home phuket</t>
+        </is>
+      </c>
+      <c r="C43" s="43" t="n">
+        <v>32606</v>
+      </c>
+      <c r="D43" s="43" t="n">
+        <v>32606</v>
+      </c>
+      <c r="E43" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="41" t="inlineStr"/>
+      <c r="G43" s="47" t="inlineStr">
+        <is>
+          <t>+103.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>c231 brand new 1br prime spot pool amp gym near beach</t>
+        </is>
+      </c>
+      <c r="C44" s="45" t="n">
+        <v>34869</v>
+      </c>
+      <c r="D44" s="45" t="n">
+        <v>34869</v>
+      </c>
+      <c r="E44" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="19" t="inlineStr"/>
+      <c r="G44" s="48" t="inlineStr">
+        <is>
+          <t>+117.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="B45" s="42" t="inlineStr">
+        <is>
+          <t>brand new 1br ozone condo panoramic windows 8557</t>
+        </is>
+      </c>
+      <c r="C45" s="43" t="n">
+        <v>36700</v>
+      </c>
+      <c r="D45" s="43" t="n">
+        <v>36700</v>
+      </c>
+      <c r="E45" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="41" t="inlineStr"/>
+      <c r="G45" s="47" t="inlineStr">
+        <is>
+          <t>+128.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>new spacious condo 1br 42m2 ozone bangtao 8686</t>
+        </is>
+      </c>
+      <c r="C46" s="45" t="n">
+        <v>36700</v>
+      </c>
+      <c r="D46" s="45" t="n">
+        <v>36700</v>
+      </c>
+      <c r="E46" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="19" t="inlineStr"/>
+      <c r="G46" s="48" t="inlineStr">
+        <is>
+          <t>+128.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="41" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="B47" s="42" t="inlineStr">
+        <is>
+          <t>ozone apartment in lagune</t>
+        </is>
+      </c>
+      <c r="C47" s="41" t="n"/>
+      <c r="D47" s="41" t="n"/>
+      <c r="E47" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="41" t="inlineStr"/>
+      <c r="G47" s="41" t="inlineStr"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>stylish-one-bedroom-apartment-in-ozone-condominium</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="n"/>
+      <c r="D48" s="19" t="n"/>
+      <c r="E48" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="19" t="inlineStr"/>
+      <c r="G48" s="19" t="inlineStr"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>★ Ozone 1BR</t>
+        </is>
+      </c>
+      <c r="C50" s="40" t="n">
+        <v>25630</v>
+      </c>
+      <c r="D50" s="40" t="n">
+        <v>25630</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="10" t="inlineStr"/>
+      <c r="G50" s="10" t="inlineStr"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="B51" s="42" t="inlineStr">
+        <is>
+          <t>brand new ozone bangtao condo by lofty</t>
+        </is>
+      </c>
+      <c r="C51" s="43" t="n">
+        <v>21783</v>
+      </c>
+      <c r="D51" s="43" t="n">
+        <v>24159</v>
+      </c>
+      <c r="E51" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="44" t="inlineStr">
+        <is>
+          <t>-15.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>the ozone bangtao by beringela</t>
+        </is>
+      </c>
+      <c r="C52" s="45" t="n">
+        <v>27027</v>
+      </c>
+      <c r="D52" s="45" t="n">
+        <v>27027</v>
+      </c>
+      <c r="E52" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="48" t="inlineStr">
+        <is>
+          <t>+5.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="41" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="B53" s="42" t="inlineStr">
+        <is>
+          <t>ozone condominium bang tao by my home phuket</t>
+        </is>
+      </c>
+      <c r="C53" s="43" t="n">
+        <v>32606</v>
+      </c>
+      <c r="D53" s="43" t="n">
+        <v>32606</v>
+      </c>
+      <c r="E53" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="41" t="inlineStr"/>
+      <c r="G53" s="47" t="inlineStr">
+        <is>
+          <t>+27.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>C235 New Modern 1BR</t>
+        </is>
+      </c>
+      <c r="C54" s="45" t="n">
+        <v>35394</v>
+      </c>
+      <c r="D54" s="45" t="n">
+        <v>35394</v>
+      </c>
+      <c r="E54" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="48" t="inlineStr">
+        <is>
+          <t>+38.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="41" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="B55" s="42" t="inlineStr">
+        <is>
+          <t>brand new 1br ozone condo panoramic windows 8557</t>
+        </is>
+      </c>
+      <c r="C55" s="43" t="n">
+        <v>41600</v>
+      </c>
+      <c r="D55" s="43" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E55" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="41" t="inlineStr"/>
+      <c r="G55" s="47" t="inlineStr">
+        <is>
+          <t>+62.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>new spacious condo 1br 42m2 ozone bangtao 8686</t>
+        </is>
+      </c>
+      <c r="C56" s="45" t="n">
+        <v>41600</v>
+      </c>
+      <c r="D56" s="45" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E56" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="19" t="inlineStr"/>
+      <c r="G56" s="48" t="inlineStr">
+        <is>
+          <t>+62.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="41" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="B57" s="42" t="inlineStr">
+        <is>
+          <t>c231 brand new 1br prime spot pool amp gym near beach</t>
+        </is>
+      </c>
+      <c r="C57" s="43" t="n">
+        <v>48129</v>
+      </c>
+      <c r="D57" s="43" t="n">
+        <v>48129</v>
+      </c>
+      <c r="E57" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="41" t="inlineStr"/>
+      <c r="G57" s="47" t="inlineStr">
+        <is>
+          <t>+87.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>cozy 1 br bangtao beach</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="n"/>
+      <c r="D58" s="19" t="n"/>
+      <c r="E58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="19" t="inlineStr"/>
+      <c r="G58" s="19" t="inlineStr"/>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="41" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="B59" s="42" t="inlineStr">
+        <is>
+          <t>ozone apartment in lagune</t>
+        </is>
+      </c>
+      <c r="C59" s="41" t="n"/>
+      <c r="D59" s="41" t="n"/>
+      <c r="E59" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="41" t="inlineStr"/>
+      <c r="G59" s="41" t="inlineStr"/>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>stylish-one-bedroom-apartment-in-ozone-condominium</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="n"/>
+      <c r="D60" s="19" t="n"/>
+      <c r="E60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="19" t="inlineStr"/>
+      <c r="G60" s="19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
